--- a/data/trans_dic/P41D_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P41D_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto a la última vez que lo intentaron se quedó embarazada</t>
+          <t>Población que con respecto a la última vez que lo intentaron se quedó embarazada (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,08</t>
+          <t>0,0; 69,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,58</t>
+          <t>0,0; 83,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,37; 62,13</t>
+          <t>6,56; 63,21</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,49</t>
+          <t>0,0; 70,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,68</t>
+          <t>0,0; 47,29</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,62</t>
+          <t>0,0; 43,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,55; 60,85</t>
+          <t>9,28; 59,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,31; 41,09</t>
+          <t>7,36; 41,91</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto a la última vez que lo intentaron se quedó embarazada</t>
+          <t>Población que con respecto a la última vez que lo intentaron se quedó embarazada (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -884,12 +884,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 538</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 538</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5113</t>
+          <t>0; 4992</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3055</t>
+          <t>0; 3045</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>691; 6740</t>
+          <t>711; 6857</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2217</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4998</t>
+          <t>0; 5092</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5812</t>
+          <t>0; 6293</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6071</t>
+          <t>0; 5732</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>986; 7024</t>
+          <t>1071; 6917</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1816; 10213</t>
+          <t>1830; 10417</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P41D_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P41D_2023-Estudios-trans_dic.xlsx
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,39</t>
+          <t>0,0; 68,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,32</t>
+          <t>0,0; 86,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,56; 63,21</t>
+          <t>6,67; 59,83</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,8</t>
+          <t>0,0; 68,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,29</t>
+          <t>0,0; 44,97</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,08</t>
+          <t>0,0; 41,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,28; 59,91</t>
+          <t>8,52; 61,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,36; 41,91</t>
+          <t>6,77; 40,57</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1508</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2821</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4992</t>
+          <t>0; 5010</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3045</t>
+          <t>0; 3199</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>711; 6857</t>
+          <t>736; 6603</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2073</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5092</t>
+          <t>0; 5136</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6293</t>
+          <t>0; 6431</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4893</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5732</t>
+          <t>0; 5855</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1071; 6917</t>
+          <t>1012; 7250</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1830; 10417</t>
+          <t>1765; 10568</t>
         </is>
       </c>
     </row>
